--- a/docentes/Cruz Alejo José Armando - Estadisticos 20212.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20212.xlsx
@@ -465,16 +465,19 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +533,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -589,16 +592,19 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20212.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20212.xlsx
@@ -530,16 +530,19 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>32</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20212.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20212.xlsx
@@ -607,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
